--- a/artfynd/A 45412-2025 artfynd.xlsx
+++ b/artfynd/A 45412-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128340023</v>
       </c>
       <c r="B2" t="n">
-        <v>92742</v>
+        <v>92754</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>128340027</v>
       </c>
       <c r="B3" t="n">
-        <v>92742</v>
+        <v>92754</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>128340022</v>
       </c>
       <c r="B4" t="n">
-        <v>78840</v>
+        <v>78844</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 45412-2025 artfynd.xlsx
+++ b/artfynd/A 45412-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128340023</v>
       </c>
       <c r="B2" t="n">
-        <v>92754</v>
+        <v>92756</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>128340027</v>
       </c>
       <c r="B3" t="n">
-        <v>92754</v>
+        <v>92756</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>128340022</v>
       </c>
       <c r="B4" t="n">
-        <v>78844</v>
+        <v>78846</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 45412-2025 artfynd.xlsx
+++ b/artfynd/A 45412-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -991,6 +991,685 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>128791268</v>
+      </c>
+      <c r="B5" t="n">
+        <v>92756</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Tjädermyrslyet, Nb</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>769469</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7288672</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>128791269</v>
+      </c>
+      <c r="B6" t="n">
+        <v>92756</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Tjädermyrslyet, Nb</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>769477</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7288684</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>128791235</v>
+      </c>
+      <c r="B7" t="n">
+        <v>90499</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>1962</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Vaddporing</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Anomoporia kamtschatica</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Parmasto) Bondartseva</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Tjädermyrslyet, Nb</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>769479</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7288694</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>128791265</v>
+      </c>
+      <c r="B8" t="n">
+        <v>79089</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Tjädermyrslyet, Nb</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>769501</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7288648</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>128791232</v>
+      </c>
+      <c r="B9" t="n">
+        <v>79708</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Tjädermyrslyet, Nb</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>769448</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7288692</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>128791247</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79113</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6434</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Nästlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Bryoria furcellata</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Tjädermyrslyet, Nb</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>769480</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7288693</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>128791234</v>
+      </c>
+      <c r="B11" t="n">
+        <v>90499</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>1962</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Vaddporing</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Anomoporia kamtschatica</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Parmasto) Bondartseva</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Tjädermyrslyet, Nb</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>769466</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7288672</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 45412-2025 artfynd.xlsx
+++ b/artfynd/A 45412-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128340023</v>
       </c>
       <c r="B2" t="n">
-        <v>92756</v>
+        <v>92757</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>128340027</v>
       </c>
       <c r="B3" t="n">
-        <v>92756</v>
+        <v>92757</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>128791268</v>
       </c>
       <c r="B5" t="n">
-        <v>92756</v>
+        <v>92757</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1093,7 +1093,7 @@
         <v>128791269</v>
       </c>
       <c r="B6" t="n">
-        <v>92756</v>
+        <v>92757</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 45412-2025 artfynd.xlsx
+++ b/artfynd/A 45412-2025 artfynd.xlsx
@@ -996,7 +996,7 @@
         <v>128791268</v>
       </c>
       <c r="B5" t="n">
-        <v>92757</v>
+        <v>92784</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1093,7 +1093,7 @@
         <v>128791269</v>
       </c>
       <c r="B6" t="n">
-        <v>92757</v>
+        <v>92784</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
         <v>128791235</v>
       </c>
       <c r="B7" t="n">
-        <v>90499</v>
+        <v>90526</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1287,7 +1287,7 @@
         <v>128791265</v>
       </c>
       <c r="B8" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1381,32 +1381,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128791232</v>
+        <v>128791247</v>
       </c>
       <c r="B9" t="n">
-        <v>79708</v>
+        <v>79140</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>6434</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1416,10 +1416,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>769448</v>
+        <v>769480</v>
       </c>
       <c r="R9" t="n">
-        <v>7288692</v>
+        <v>7288693</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1478,32 +1478,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128791247</v>
+        <v>128791232</v>
       </c>
       <c r="B10" t="n">
-        <v>79113</v>
+        <v>79735</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6434</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1513,10 +1513,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>769480</v>
+        <v>769448</v>
       </c>
       <c r="R10" t="n">
-        <v>7288693</v>
+        <v>7288692</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1578,7 +1578,7 @@
         <v>128791234</v>
       </c>
       <c r="B11" t="n">
-        <v>90499</v>
+        <v>90526</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 45412-2025 artfynd.xlsx
+++ b/artfynd/A 45412-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128340023</v>
       </c>
       <c r="B2" t="n">
-        <v>92757</v>
+        <v>92784</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>128340027</v>
       </c>
       <c r="B3" t="n">
-        <v>92757</v>
+        <v>92784</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>128340022</v>
       </c>
       <c r="B4" t="n">
-        <v>78846</v>
+        <v>78873</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1381,32 +1381,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128791247</v>
+        <v>128791232</v>
       </c>
       <c r="B9" t="n">
-        <v>79140</v>
+        <v>79735</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6434</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1416,10 +1416,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>769480</v>
+        <v>769448</v>
       </c>
       <c r="R9" t="n">
-        <v>7288693</v>
+        <v>7288692</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1478,32 +1478,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128791232</v>
+        <v>128791247</v>
       </c>
       <c r="B10" t="n">
-        <v>79735</v>
+        <v>79140</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>6434</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1513,10 +1513,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>769448</v>
+        <v>769480</v>
       </c>
       <c r="R10" t="n">
-        <v>7288692</v>
+        <v>7288693</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>

--- a/artfynd/A 45412-2025 artfynd.xlsx
+++ b/artfynd/A 45412-2025 artfynd.xlsx
@@ -996,7 +996,7 @@
         <v>128791268</v>
       </c>
       <c r="B5" t="n">
-        <v>92784</v>
+        <v>92789</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1093,7 +1093,7 @@
         <v>128791269</v>
       </c>
       <c r="B6" t="n">
-        <v>92784</v>
+        <v>92789</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
         <v>128791235</v>
       </c>
       <c r="B7" t="n">
-        <v>90526</v>
+        <v>90531</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1287,7 +1287,7 @@
         <v>128791265</v>
       </c>
       <c r="B8" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
         <v>128791232</v>
       </c>
       <c r="B9" t="n">
-        <v>79735</v>
+        <v>79739</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1481,7 +1481,7 @@
         <v>128791247</v>
       </c>
       <c r="B10" t="n">
-        <v>79140</v>
+        <v>79144</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1578,7 +1578,7 @@
         <v>128791234</v>
       </c>
       <c r="B11" t="n">
-        <v>90526</v>
+        <v>90531</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 45412-2025 artfynd.xlsx
+++ b/artfynd/A 45412-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128340023</v>
       </c>
       <c r="B2" t="n">
-        <v>92784</v>
+        <v>92794</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>128340027</v>
       </c>
       <c r="B3" t="n">
-        <v>92784</v>
+        <v>92794</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>128340022</v>
       </c>
       <c r="B4" t="n">
-        <v>78873</v>
+        <v>78877</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>128791268</v>
       </c>
       <c r="B5" t="n">
-        <v>92789</v>
+        <v>92794</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1093,7 +1093,7 @@
         <v>128791269</v>
       </c>
       <c r="B6" t="n">
-        <v>92789</v>
+        <v>92794</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
         <v>128791235</v>
       </c>
       <c r="B7" t="n">
-        <v>90531</v>
+        <v>90536</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1381,32 +1381,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128791232</v>
+        <v>128791247</v>
       </c>
       <c r="B9" t="n">
-        <v>79739</v>
+        <v>79144</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>6434</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1416,10 +1416,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>769448</v>
+        <v>769480</v>
       </c>
       <c r="R9" t="n">
-        <v>7288692</v>
+        <v>7288693</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1478,32 +1478,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128791247</v>
+        <v>128791232</v>
       </c>
       <c r="B10" t="n">
-        <v>79144</v>
+        <v>79739</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6434</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1513,10 +1513,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>769480</v>
+        <v>769448</v>
       </c>
       <c r="R10" t="n">
-        <v>7288693</v>
+        <v>7288692</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1578,7 +1578,7 @@
         <v>128791234</v>
       </c>
       <c r="B11" t="n">
-        <v>90531</v>
+        <v>90536</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 45412-2025 artfynd.xlsx
+++ b/artfynd/A 45412-2025 artfynd.xlsx
@@ -1381,32 +1381,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128791247</v>
+        <v>128791232</v>
       </c>
       <c r="B9" t="n">
-        <v>79144</v>
+        <v>79739</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6434</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1416,10 +1416,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>769480</v>
+        <v>769448</v>
       </c>
       <c r="R9" t="n">
-        <v>7288693</v>
+        <v>7288692</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1478,32 +1478,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128791232</v>
+        <v>128791247</v>
       </c>
       <c r="B10" t="n">
-        <v>79739</v>
+        <v>79144</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>6434</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1513,10 +1513,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>769448</v>
+        <v>769480</v>
       </c>
       <c r="R10" t="n">
-        <v>7288692</v>
+        <v>7288693</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>

--- a/artfynd/A 45412-2025 artfynd.xlsx
+++ b/artfynd/A 45412-2025 artfynd.xlsx
@@ -1381,32 +1381,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128791232</v>
+        <v>128791247</v>
       </c>
       <c r="B9" t="n">
-        <v>79739</v>
+        <v>79144</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>6434</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1416,10 +1416,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>769448</v>
+        <v>769480</v>
       </c>
       <c r="R9" t="n">
-        <v>7288692</v>
+        <v>7288693</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1478,32 +1478,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128791247</v>
+        <v>128791232</v>
       </c>
       <c r="B10" t="n">
-        <v>79144</v>
+        <v>79739</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6434</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1513,10 +1513,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>769480</v>
+        <v>769448</v>
       </c>
       <c r="R10" t="n">
-        <v>7288693</v>
+        <v>7288692</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>

--- a/artfynd/A 45412-2025 artfynd.xlsx
+++ b/artfynd/A 45412-2025 artfynd.xlsx
@@ -996,7 +996,7 @@
         <v>128791268</v>
       </c>
       <c r="B5" t="n">
-        <v>92794</v>
+        <v>92798</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1093,7 +1093,7 @@
         <v>128791269</v>
       </c>
       <c r="B6" t="n">
-        <v>92794</v>
+        <v>92798</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
         <v>128791235</v>
       </c>
       <c r="B7" t="n">
-        <v>90536</v>
+        <v>90540</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1287,7 +1287,7 @@
         <v>128791265</v>
       </c>
       <c r="B8" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
         <v>128791247</v>
       </c>
       <c r="B9" t="n">
-        <v>79144</v>
+        <v>79148</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1481,7 +1481,7 @@
         <v>128791232</v>
       </c>
       <c r="B10" t="n">
-        <v>79739</v>
+        <v>79743</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1578,7 +1578,7 @@
         <v>128791234</v>
       </c>
       <c r="B11" t="n">
-        <v>90536</v>
+        <v>90540</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 45412-2025 artfynd.xlsx
+++ b/artfynd/A 45412-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128340023</v>
       </c>
       <c r="B2" t="n">
-        <v>92794</v>
+        <v>92798</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>128340027</v>
       </c>
       <c r="B3" t="n">
-        <v>92794</v>
+        <v>92798</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>128340022</v>
       </c>
       <c r="B4" t="n">
-        <v>78877</v>
+        <v>78881</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 45412-2025 artfynd.xlsx
+++ b/artfynd/A 45412-2025 artfynd.xlsx
@@ -1381,32 +1381,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128791247</v>
+        <v>128791232</v>
       </c>
       <c r="B9" t="n">
-        <v>79148</v>
+        <v>79743</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6434</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1416,10 +1416,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>769480</v>
+        <v>769448</v>
       </c>
       <c r="R9" t="n">
-        <v>7288693</v>
+        <v>7288692</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1478,32 +1478,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128791232</v>
+        <v>128791247</v>
       </c>
       <c r="B10" t="n">
-        <v>79743</v>
+        <v>79148</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>6434</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1513,10 +1513,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>769448</v>
+        <v>769480</v>
       </c>
       <c r="R10" t="n">
-        <v>7288692</v>
+        <v>7288693</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>

--- a/artfynd/A 45412-2025 artfynd.xlsx
+++ b/artfynd/A 45412-2025 artfynd.xlsx
@@ -996,7 +996,7 @@
         <v>128791268</v>
       </c>
       <c r="B5" t="n">
-        <v>92798</v>
+        <v>92803</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1093,7 +1093,7 @@
         <v>128791269</v>
       </c>
       <c r="B6" t="n">
-        <v>92798</v>
+        <v>92803</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
         <v>128791235</v>
       </c>
       <c r="B7" t="n">
-        <v>90540</v>
+        <v>90545</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1287,7 +1287,7 @@
         <v>128791265</v>
       </c>
       <c r="B8" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
         <v>128791232</v>
       </c>
       <c r="B9" t="n">
-        <v>79743</v>
+        <v>79648</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1481,7 +1481,7 @@
         <v>128791247</v>
       </c>
       <c r="B10" t="n">
-        <v>79148</v>
+        <v>79053</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1578,7 +1578,7 @@
         <v>128791234</v>
       </c>
       <c r="B11" t="n">
-        <v>90540</v>
+        <v>90545</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 45412-2025 artfynd.xlsx
+++ b/artfynd/A 45412-2025 artfynd.xlsx
@@ -996,7 +996,7 @@
         <v>128791268</v>
       </c>
       <c r="B5" t="n">
-        <v>92811</v>
+        <v>92816</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1093,7 +1093,7 @@
         <v>128791269</v>
       </c>
       <c r="B6" t="n">
-        <v>92811</v>
+        <v>92816</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
         <v>128791235</v>
       </c>
       <c r="B7" t="n">
-        <v>90552</v>
+        <v>90555</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1578,7 +1578,7 @@
         <v>128791234</v>
       </c>
       <c r="B11" t="n">
-        <v>90552</v>
+        <v>90555</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 45412-2025 artfynd.xlsx
+++ b/artfynd/A 45412-2025 artfynd.xlsx
@@ -996,7 +996,7 @@
         <v>128791268</v>
       </c>
       <c r="B5" t="n">
-        <v>92816</v>
+        <v>92819</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1093,7 +1093,7 @@
         <v>128791269</v>
       </c>
       <c r="B6" t="n">
-        <v>92816</v>
+        <v>92819</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
         <v>128791235</v>
       </c>
       <c r="B7" t="n">
-        <v>90555</v>
+        <v>90558</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1287,7 +1287,7 @@
         <v>128791265</v>
       </c>
       <c r="B8" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1381,32 +1381,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128791232</v>
+        <v>128791247</v>
       </c>
       <c r="B9" t="n">
-        <v>79653</v>
+        <v>79059</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>6434</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1416,10 +1416,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>769448</v>
+        <v>769480</v>
       </c>
       <c r="R9" t="n">
-        <v>7288692</v>
+        <v>7288693</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1478,32 +1478,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128791247</v>
+        <v>128791232</v>
       </c>
       <c r="B10" t="n">
-        <v>79058</v>
+        <v>79654</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6434</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1513,10 +1513,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>769480</v>
+        <v>769448</v>
       </c>
       <c r="R10" t="n">
-        <v>7288693</v>
+        <v>7288692</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1578,7 +1578,7 @@
         <v>128791234</v>
       </c>
       <c r="B11" t="n">
-        <v>90555</v>
+        <v>90558</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 45412-2025 artfynd.xlsx
+++ b/artfynd/A 45412-2025 artfynd.xlsx
@@ -1381,32 +1381,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128791247</v>
+        <v>128791232</v>
       </c>
       <c r="B9" t="n">
-        <v>79059</v>
+        <v>79654</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6434</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1416,10 +1416,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>769480</v>
+        <v>769448</v>
       </c>
       <c r="R9" t="n">
-        <v>7288693</v>
+        <v>7288692</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1478,32 +1478,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128791232</v>
+        <v>128791247</v>
       </c>
       <c r="B10" t="n">
-        <v>79654</v>
+        <v>79059</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>6434</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1513,10 +1513,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>769448</v>
+        <v>769480</v>
       </c>
       <c r="R10" t="n">
-        <v>7288692</v>
+        <v>7288693</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>

--- a/artfynd/A 45412-2025 artfynd.xlsx
+++ b/artfynd/A 45412-2025 artfynd.xlsx
@@ -996,7 +996,7 @@
         <v>128791268</v>
       </c>
       <c r="B5" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1093,7 +1093,7 @@
         <v>128791269</v>
       </c>
       <c r="B6" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
         <v>128791235</v>
       </c>
       <c r="B7" t="n">
-        <v>90558</v>
+        <v>90562</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1287,7 +1287,7 @@
         <v>128791265</v>
       </c>
       <c r="B8" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
         <v>128791232</v>
       </c>
       <c r="B9" t="n">
-        <v>79654</v>
+        <v>79658</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1481,7 +1481,7 @@
         <v>128791247</v>
       </c>
       <c r="B10" t="n">
-        <v>79059</v>
+        <v>79063</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1578,7 +1578,7 @@
         <v>128791234</v>
       </c>
       <c r="B11" t="n">
-        <v>90558</v>
+        <v>90562</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 45412-2025 artfynd.xlsx
+++ b/artfynd/A 45412-2025 artfynd.xlsx
@@ -996,7 +996,7 @@
         <v>128791268</v>
       </c>
       <c r="B5" t="n">
-        <v>92826</v>
+        <v>92833</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1093,7 +1093,7 @@
         <v>128791269</v>
       </c>
       <c r="B6" t="n">
-        <v>92826</v>
+        <v>92833</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
         <v>128791235</v>
       </c>
       <c r="B7" t="n">
-        <v>90562</v>
+        <v>90569</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1381,32 +1381,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128791232</v>
+        <v>128791247</v>
       </c>
       <c r="B9" t="n">
-        <v>79658</v>
+        <v>79063</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>6434</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1416,10 +1416,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>769448</v>
+        <v>769480</v>
       </c>
       <c r="R9" t="n">
-        <v>7288692</v>
+        <v>7288693</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1478,32 +1478,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128791247</v>
+        <v>128791232</v>
       </c>
       <c r="B10" t="n">
-        <v>79063</v>
+        <v>79658</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6434</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1513,10 +1513,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>769480</v>
+        <v>769448</v>
       </c>
       <c r="R10" t="n">
-        <v>7288693</v>
+        <v>7288692</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1578,7 +1578,7 @@
         <v>128791234</v>
       </c>
       <c r="B11" t="n">
-        <v>90562</v>
+        <v>90569</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 45412-2025 artfynd.xlsx
+++ b/artfynd/A 45412-2025 artfynd.xlsx
@@ -996,7 +996,7 @@
         <v>128791268</v>
       </c>
       <c r="B5" t="n">
-        <v>92833</v>
+        <v>92835</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1093,7 +1093,7 @@
         <v>128791269</v>
       </c>
       <c r="B6" t="n">
-        <v>92833</v>
+        <v>92835</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
         <v>128791235</v>
       </c>
       <c r="B7" t="n">
-        <v>90569</v>
+        <v>90571</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1287,7 +1287,7 @@
         <v>128791265</v>
       </c>
       <c r="B8" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
         <v>128791247</v>
       </c>
       <c r="B9" t="n">
-        <v>79063</v>
+        <v>79065</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1481,7 +1481,7 @@
         <v>128791232</v>
       </c>
       <c r="B10" t="n">
-        <v>79658</v>
+        <v>79660</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1578,7 +1578,7 @@
         <v>128791234</v>
       </c>
       <c r="B11" t="n">
-        <v>90569</v>
+        <v>90571</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 45412-2025 artfynd.xlsx
+++ b/artfynd/A 45412-2025 artfynd.xlsx
@@ -1381,32 +1381,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128791247</v>
+        <v>128791232</v>
       </c>
       <c r="B9" t="n">
-        <v>79065</v>
+        <v>79660</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6434</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1416,10 +1416,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>769480</v>
+        <v>769448</v>
       </c>
       <c r="R9" t="n">
-        <v>7288693</v>
+        <v>7288692</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1478,32 +1478,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128791232</v>
+        <v>128791247</v>
       </c>
       <c r="B10" t="n">
-        <v>79660</v>
+        <v>79065</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>6434</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1513,10 +1513,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>769448</v>
+        <v>769480</v>
       </c>
       <c r="R10" t="n">
-        <v>7288692</v>
+        <v>7288693</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>

--- a/artfynd/A 45412-2025 artfynd.xlsx
+++ b/artfynd/A 45412-2025 artfynd.xlsx
@@ -996,7 +996,7 @@
         <v>128791268</v>
       </c>
       <c r="B5" t="n">
-        <v>92835</v>
+        <v>92821</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1093,7 +1093,7 @@
         <v>128791269</v>
       </c>
       <c r="B6" t="n">
-        <v>92835</v>
+        <v>92821</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
         <v>128791235</v>
       </c>
       <c r="B7" t="n">
-        <v>90571</v>
+        <v>90572</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1578,7 +1578,7 @@
         <v>128791234</v>
       </c>
       <c r="B11" t="n">
-        <v>90571</v>
+        <v>90572</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
